--- a/ci-build/ValueSet-onko-service-request-kontext.xlsx
+++ b/ci-build/ValueSet-onko-service-request-kontext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:11:39+00:00</t>
+    <t>2026-09-28T20:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-service-request-kontext.xlsx
+++ b/ci-build/ValueSet-onko-service-request-kontext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T20:57:11+00:00</t>
+    <t>2026-09-28T21:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-service-request-kontext.xlsx
+++ b/ci-build/ValueSet-onko-service-request-kontext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T21:01:12+00:00</t>
+    <t>2026-09-30T11:29:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-service-request-kontext.xlsx
+++ b/ci-build/ValueSet-onko-service-request-kontext.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:29:35+00:00</t>
+    <t>2026-10-01T05:55:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,7 +86,11 @@
   <si>
     <t>Zusätzlicher Kontext eines Behandlungsschritts – ergänzend zur Therapieintention – z. B. ob eine
 Maßnahme lokal begrenzt, symptomatisch, präventiv, definitiv, additiv, intraoperativ, elektiv
-oder im Notfall erfolgt. Gebunden an die Extension `onko-behandlungs-kontext`.</t>
+oder im Notfall erfolgt. Gebunden an die Extension `onko-behandlungs-kontext`.
+**Stellung zur Operation:** Die Codes `Neoadjuvant intent`, `Adjuvant - intent`, `Additive` und
+`Intraoperative` decken die Achse ab, die das MII-Modul Onkologie als
+`mii-cs-onko-therapie-stellungzurop` (A/N/I/Z) führt. Sie stehen hier und nicht in der
+Intentions-Liste, weil sie die Intention ergänzen statt sie zu ersetzen.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -126,6 +130,18 @@
   </si>
   <si>
     <t>Definitive (qualifier value)</t>
+  </si>
+  <si>
+    <t>373847000</t>
+  </si>
+  <si>
+    <t>Neoadjuvant intent</t>
+  </si>
+  <si>
+    <t>373846009</t>
+  </si>
+  <si>
+    <t>Adjuvant - intent</t>
   </si>
   <si>
     <t>260364009</t>
@@ -422,7 +438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -506,15 +522,31 @@
         <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/ci-build/ValueSet-onko-service-request-kontext.xlsx
+++ b/ci-build/ValueSet-onko-service-request-kontext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T05:55:59+00:00</t>
+    <t>2026-10-01T06:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-service-request-kontext.xlsx
+++ b/ci-build/ValueSet-onko-service-request-kontext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T06:38:06+00:00</t>
+    <t>2026-10-01T08:23:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-service-request-kontext.xlsx
+++ b/ci-build/ValueSet-onko-service-request-kontext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:23:16+00:00</t>
+    <t>2026-10-01T11:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-service-request-kontext.xlsx
+++ b/ci-build/ValueSet-onko-service-request-kontext.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:19:09+00:00</t>
+    <t>2026-10-01T11:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
